--- a/output/pdf_financials_xlsx/LUCA.xlsx
+++ b/output/pdf_financials_xlsx/LUCA.xlsx
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-1.338941</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-1.532</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>-1.964</v>
@@ -5831,22 +5831,22 @@
         <v>2.791046</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>3.05951</v>
+        <v>1.275246</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.448678</v>
+        <v>1.048761</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.37477</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.579552</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.895962</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.161752</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -5867,16 +5867,16 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.573</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.564</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>12.673</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="93">
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.538927</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -11050,7 +11050,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -14122,7 +14126,11 @@
           <t>Reserves 18 12,673</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -16023,7 +16031,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -25237,7 +25249,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -27237,7 +27253,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28249,7 +28269,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -32133,7 +32157,11 @@
           <t>Share-based payments reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -33580,7 +33608,11 @@
           <t>Share-based payments reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -34069,7 +34101,11 @@
           <t>Share-based payments reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -34570,7 +34606,11 @@
           <t>Share-based payments reserve (Notes 13 and 14)</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -44782,7 +44822,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -54008,7 +54048,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -72367,7 +72407,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -84432,7 +84472,7 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
@@ -86452,7 +86492,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">

--- a/output/pdf_financials_xlsx/LUCA.xlsx
+++ b/output/pdf_financials_xlsx/LUCA.xlsx
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.07452</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00759</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000304</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003873</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003738</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005509999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.422</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.233</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1991,25 +1991,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.248776</v>
+        <v>-1.323296</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.320274</v>
+        <v>-1.327864</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.508593</v>
+        <v>-1.508897</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.725501</v>
+        <v>-3.729374</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.657888</v>
+        <v>-1.661626</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.382818</v>
+        <v>-1.383369</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.697039</v>
+        <v>-0.697124</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.769638</v>
@@ -2024,13 +2024,13 @@
         <v>-29.341</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-11.624</v>
+        <v>-11.585</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>36.265</v>
+        <v>36.687</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-11.607</v>
+        <v>-11.374</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-14.996</v>
@@ -2107,25 +2107,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.248776</v>
+        <v>-1.323296</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.320274</v>
+        <v>-1.327864</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.508593</v>
+        <v>-1.508897</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.725501</v>
+        <v>-3.729374</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.657888</v>
+        <v>-1.661626</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.382818</v>
+        <v>-1.383369</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.697039</v>
+        <v>-0.697124</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.742558</v>
@@ -2140,13 +2140,13 @@
         <v>-28.339</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-11.179</v>
+        <v>-11.14</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>36.803</v>
+        <v>37.225</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-9.156000000000001</v>
+        <v>-8.923</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-11.694</v>
@@ -2216,13 +2216,13 @@
         <v>-137.5612834328431</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-48.2748197089433</v>
+        <v>-48.10640411106793</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>52.81413236897997</v>
+        <v>53.41972332242696</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-10.25411295651297</v>
+        <v>-9.993168404430458</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-11.54848903811969</v>
@@ -2382,46 +2382,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.647613</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.25336</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.49244</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.08534799999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.026882</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.02238</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000446</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.489614</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>11.997057</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.049</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.152</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.85</v>
@@ -2498,46 +2498,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.647613</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.25336</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.49244</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.08534799999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.026882</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.02238</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000446</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.489614</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>11.997057</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>5.296</v>
+        <v>5.412</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>4.653</v>
+        <v>4.798</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>4.271</v>
+        <v>4.528</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>3.909</v>
+        <v>6.958</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.152</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.85</v>
@@ -3194,46 +3194,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.658446</v>
+        <v>0.010833</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.280196</v>
+        <v>0.026836</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.522436</v>
+        <v>0.029996</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.16042</v>
+        <v>0.075072</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.040732</v>
+        <v>0.01385</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.034238</v>
+        <v>0.011858</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002219</v>
+        <v>0.001773</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.85831</v>
+        <v>0.368696</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>12.151948</v>
+        <v>0.154891</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.903</v>
+        <v>0.787</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.416</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.016</v>
+        <v>1.759</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>6.561</v>
+        <v>3.512</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.994</v>
+        <v>3.842</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>2.837</v>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -28774,7 +28774,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -32462,7 +32462,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -34907,7 +34907,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E266" s="5" t="n">
@@ -73575,7 +73575,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -77379,7 +77379,7 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -81270,7 +81270,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
@@ -96934,7 +96934,7 @@
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -98908,7 +98908,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -100423,7 +100423,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E920" s="5" t="n">
